--- a/results/MVSE/dblp/MVSE_dblp<l01>AllRes_90.46.xlsx
+++ b/results/MVSE/dblp/MVSE_dblp<l01>AllRes_90.46.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:U87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,78 +476,93 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>walk_hop</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>avg_loss</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>avg_test_mif1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>std_loss</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>std_test_mif1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>config2str</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>nce_k</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>avg_loss</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>avg_test_mif1</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>std_loss</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>std_test_mif1</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>config2str</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>walk_hop</t>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ge_layer</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>train_mode</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>num_samples</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>128</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H2" t="n">
         <v>10</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>MVSE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>MPRW</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>dblp</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>NCEK</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>128</v>
-      </c>
-      <c r="G2" t="n">
-        <v>500</v>
-      </c>
-      <c r="H2" t="n">
-        <v>50</v>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>mp_spec</t>
@@ -555,14 +570,14 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>WL_0_0_1</t>
+          <t>WL_0.45_0.45_0.1</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0.26</v>
@@ -578,16 +593,27 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-09_34_53', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'mode', 'dataset', 'train_percentage', 'p_epoch', 'f_epoch', 'batch_size', 'ge_layer', 'aug_mode', 'cl_mode', 'skip_pretrain', 'walk_hop', 'eval_freq', 'train_mode', 'print_freq', 'seed', 'ge_mode', 'nce_k', 'num_copies', 'num_samples'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_20-10_17_59', 'cl_mode': 'WL_0.45_0.45_0.1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'default', 'f_epoch': 10, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 2, 'p_epoch': 3000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 0, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>4096</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -613,7 +639,7 @@
         <v>128</v>
       </c>
       <c r="G3" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="H3" t="n">
         <v>50</v>
@@ -629,7 +655,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
         <v>2</v>
@@ -638,26 +664,37 @@
         <v>0.26</v>
       </c>
       <c r="N3" t="n">
-        <v>90.3</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="P3" t="n">
-        <v>0.36</v>
+        <v>0.74</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_21-02_11_03', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-09_34_53', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>4096</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -676,14 +713,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>WH</t>
+          <t>NCEK</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>128</v>
       </c>
       <c r="G4" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="H4" t="n">
         <v>50</v>
@@ -699,35 +736,46 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="N4" t="n">
-        <v>90.16</v>
+        <v>90.3</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.36</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_21-03_19_05', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 3000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_21-02_11_03', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>4096</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -746,17 +794,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>WH</t>
+          <t>default</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>128</v>
       </c>
       <c r="G5" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="H5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -765,39 +813,50 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>WL_0_0_1</t>
+          <t>WL_0.1_0.1_0.8</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="N5" t="n">
-        <v>90.11</v>
+        <v>90.3</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="P5" t="n">
-        <v>0.76</v>
+        <v>0.36</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_21-03_10_02', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'mode', 'dataset', 'train_percentage', 'p_epoch', 'f_epoch', 'batch_size', 'ge_layer', 'aug_mode', 'cl_mode', 'skip_pretrain', 'walk_hop', 'eval_freq', 'train_mode', 'print_freq', 'seed', 'ge_mode', 'nce_k', 'num_copies', 'num_samples'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_22-17_40_49', 'cl_mode': 'WL_0.1_0.1_0.8', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'default', 'f_epoch': 10, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 2, 'p_epoch': 3000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 0, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>4096</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -816,14 +875,14 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NCEK</t>
+          <t>WH</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>128</v>
       </c>
       <c r="G6" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="H6" t="n">
         <v>50</v>
@@ -839,35 +898,46 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="N6" t="n">
-        <v>90.09999999999999</v>
+        <v>90.16</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="P6" t="n">
-        <v>0.41</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_21-02_22_39', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_21-03_19_05', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 3000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>4096</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -886,14 +956,14 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NCEK</t>
+          <t>WH</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>128</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="H7" t="n">
         <v>50</v>
@@ -909,35 +979,46 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="N7" t="n">
-        <v>89.98</v>
+        <v>90.11</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="P7" t="n">
-        <v>0.24</v>
+        <v>0.76</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-08_54_51', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_21-03_10_02', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>4096</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -963,7 +1044,7 @@
         <v>128</v>
       </c>
       <c r="G8" t="n">
-        <v>200</v>
+        <v>2500</v>
       </c>
       <c r="H8" t="n">
         <v>50</v>
@@ -979,35 +1060,46 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="N8" t="n">
-        <v>89.93000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="P8" t="n">
-        <v>0.68</v>
+        <v>0.41</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-09_09_56', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 200, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_21-02_22_39', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>4096</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1033,7 +1125,7 @@
         <v>128</v>
       </c>
       <c r="G9" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
         <v>50</v>
@@ -1049,35 +1141,46 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="N9" t="n">
-        <v>89.90000000000001</v>
+        <v>89.98</v>
       </c>
       <c r="O9" t="n">
         <v>0.02</v>
       </c>
       <c r="P9" t="n">
-        <v>0.46</v>
+        <v>0.24</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-08_38_33', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-08_54_51', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>4096</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1119,35 +1222,46 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>8192</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="N10" t="n">
-        <v>89.88</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="P10" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-07_32_58', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 8192, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 200, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-09_09_56', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 200, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>4096</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1166,14 +1280,14 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>WH</t>
+          <t>NCEK</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>128</v>
       </c>
       <c r="G11" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="H11" t="n">
         <v>50</v>
@@ -1189,35 +1303,46 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="N11" t="n">
-        <v>89.88</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="P11" t="n">
-        <v>0.27</v>
+        <v>0.46</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_21-02_59_21', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-08_38_33', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>4096</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1236,14 +1361,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>WH</t>
+          <t>NCEK</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>128</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="H12" t="n">
         <v>50</v>
@@ -1259,35 +1384,46 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="N12" t="n">
-        <v>89.86</v>
+        <v>89.88</v>
       </c>
       <c r="O12" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="P12" t="n">
-        <v>0.82</v>
+        <v>0.66</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-11_33_18', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-07_32_58', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 8192, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 200, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>8192</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1306,17 +1442,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>WH</t>
+          <t>default</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>128</v>
       </c>
       <c r="G13" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="H13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1325,39 +1461,50 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>WL_0_0_1</t>
+          <t>WL_0.15_0.15_0.7</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="N13" t="n">
-        <v>89.84</v>
+        <v>89.88</v>
       </c>
       <c r="O13" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="P13" t="n">
-        <v>1.02</v>
+        <v>0.27</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-11_47_19', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'mode', 'dataset', 'train_percentage', 'p_epoch', 'f_epoch', 'batch_size', 'ge_layer', 'aug_mode', 'cl_mode', 'skip_pretrain', 'walk_hop', 'eval_freq', 'train_mode', 'print_freq', 'seed', 'ge_mode', 'nce_k', 'num_copies', 'num_samples'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_20-10_11_18', 'cl_mode': 'WL_0.15_0.15_0.7', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'default', 'f_epoch': 10, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 2, 'p_epoch': 3000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 0, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>4096</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1383,7 +1530,7 @@
         <v>128</v>
       </c>
       <c r="G14" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="H14" t="n">
         <v>50</v>
@@ -1399,35 +1546,46 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="N14" t="n">
-        <v>89.79000000000001</v>
+        <v>89.88</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="P14" t="n">
-        <v>0.14</v>
+        <v>0.27</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-10_52_15', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_21-02_59_21', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>4096</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1453,7 +1611,7 @@
         <v>128</v>
       </c>
       <c r="G15" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
         <v>50</v>
@@ -1469,35 +1627,46 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="N15" t="n">
-        <v>89.48999999999999</v>
+        <v>89.86</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="P15" t="n">
-        <v>0.58</v>
+        <v>0.82</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-10_36_42', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 100, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-11_33_18', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>4096</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1523,7 +1692,7 @@
         <v>128</v>
       </c>
       <c r="G16" t="n">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="H16" t="n">
         <v>50</v>
@@ -1539,35 +1708,46 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="N16" t="n">
-        <v>89.39</v>
+        <v>89.84</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="P16" t="n">
-        <v>0.45</v>
+        <v>1.02</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-11_17_44', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 200, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-11_47_19', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>4096</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1586,7 +1766,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NCEK</t>
+          <t>WH</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1609,35 +1789,46 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>8192</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="N17" t="n">
-        <v>89.34999999999999</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="O17" t="n">
         <v>0.01</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5</v>
+        <v>0.14</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-08_03_12', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 8192, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-10_52_15', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>4096</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1663,7 +1854,7 @@
         <v>128</v>
       </c>
       <c r="G18" t="n">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="H18" t="n">
         <v>50</v>
@@ -1679,35 +1870,46 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="N18" t="n">
-        <v>89.3</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.01</v>
+        <v>0.58</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-11_23_43', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 3, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-10_36_42', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 100, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>3</v>
+        <v>4096</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U18" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1726,14 +1928,14 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NCEK</t>
+          <t>WH</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>128</v>
       </c>
       <c r="G19" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H19" t="n">
         <v>50</v>
@@ -1749,35 +1951,46 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="N19" t="n">
-        <v>89.26000000000001</v>
+        <v>89.39</v>
       </c>
       <c r="O19" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="P19" t="n">
-        <v>0.86</v>
+        <v>0.45</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-09_50_23', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 100, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-11_17_44', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 200, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>4096</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1803,7 +2016,7 @@
         <v>128</v>
       </c>
       <c r="G20" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H20" t="n">
         <v>50</v>
@@ -1819,35 +2032,46 @@
         </is>
       </c>
       <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N20" t="n">
+        <v>89.34999999999999</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-08_03_12', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 8192, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
         <v>8192</v>
       </c>
-      <c r="L20" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="N20" t="n">
-        <v>89.20999999999999</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-08_21_33', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 8192, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 100, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
-        </is>
-      </c>
-      <c r="R20" t="n">
-        <v>2</v>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1866,17 +2090,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>WH</t>
+          <t>default</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>128</v>
       </c>
       <c r="G21" t="n">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="H21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1885,39 +2109,50 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>WL_0_0_1</t>
+          <t>WL_0.2_0.2_0.6</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="N21" t="n">
-        <v>89.19</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="O21" t="n">
         <v>0.01</v>
       </c>
       <c r="P21" t="n">
-        <v>1.64</v>
+        <v>0.5</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-12_13_43', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 3, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'mode', 'dataset', 'train_percentage', 'p_epoch', 'f_epoch', 'batch_size', 'ge_layer', 'aug_mode', 'cl_mode', 'skip_pretrain', 'walk_hop', 'eval_freq', 'train_mode', 'print_freq', 'seed', 'ge_mode', 'nce_k', 'num_copies', 'num_samples'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_22-18_07_09', 'cl_mode': 'WL_0.2_0.2_0.6', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'default', 'f_epoch': 10, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 2, 'p_epoch': 3000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 0, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>4096</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1943,7 +2178,7 @@
         <v>128</v>
       </c>
       <c r="G22" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="H22" t="n">
         <v>50</v>
@@ -1959,35 +2194,46 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>4096</v>
+        <v>3</v>
       </c>
       <c r="L22" t="n">
         <v>2</v>
       </c>
       <c r="M22" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="N22" t="n">
-        <v>89.12</v>
+        <v>89.3</v>
       </c>
       <c r="O22" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="P22" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_21-03_27_22', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 3, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-11_23_43', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 3, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>3</v>
+        <v>4096</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U22" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2013,7 +2259,7 @@
         <v>128</v>
       </c>
       <c r="G23" t="n">
-        <v>1500</v>
+        <v>100</v>
       </c>
       <c r="H23" t="n">
         <v>50</v>
@@ -2029,35 +2275,46 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>8192</v>
+        <v>2</v>
       </c>
       <c r="L23" t="n">
         <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="N23" t="n">
-        <v>89.05</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="P23" t="n">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_21-02_33_54', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 8192, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-09_50_23', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 100, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>4096</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U23" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2076,14 +2333,14 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>WH</t>
+          <t>NCEK</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>128</v>
       </c>
       <c r="G24" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H24" t="n">
         <v>50</v>
@@ -2099,35 +2356,46 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
       <c r="L24" t="n">
         <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="N24" t="n">
-        <v>88.95999999999999</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="O24" t="n">
         <v>0.02</v>
       </c>
       <c r="P24" t="n">
-        <v>0.45</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-11_55_06', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 200, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 3, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-08_21_33', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 8192, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 100, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>3</v>
+        <v>8192</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U24" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2146,17 +2414,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>WH</t>
+          <t>default</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>128</v>
       </c>
       <c r="G25" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2165,39 +2433,50 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>WL_0_0_1</t>
+          <t>WL_0.4_0.2_0.4</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.31</v>
+        <v>0.21</v>
       </c>
       <c r="N25" t="n">
-        <v>88.8</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="P25" t="n">
-        <v>1.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_21-03_35_12', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 3, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'mode', 'dataset', 'train_percentage', 'p_epoch', 'f_epoch', 'batch_size', 'ge_layer', 'aug_mode', 'cl_mode', 'skip_pretrain', 'walk_hop', 'eval_freq', 'train_mode', 'print_freq', 'seed', 'ge_mode', 'nce_k', 'num_copies', 'num_samples'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_26-04_51_39', 'cl_mode': 'WL_0.4_0.2_0.4', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'default', 'f_epoch': 10, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 2, 'p_epoch': 1000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 0, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>3</v>
+        <v>4096</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U25" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2216,14 +2495,14 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NCEK</t>
+          <t>WH</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>128</v>
       </c>
       <c r="G26" t="n">
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="H26" t="n">
         <v>50</v>
@@ -2239,35 +2518,46 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>8192</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
         <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="N26" t="n">
-        <v>88.68000000000001</v>
+        <v>89.19</v>
       </c>
       <c r="O26" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="P26" t="n">
-        <v>1.05</v>
+        <v>1.64</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_21-02_45_01', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 8192, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-12_13_43', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 3, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>4096</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U26" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2293,7 +2583,7 @@
         <v>128</v>
       </c>
       <c r="G27" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="H27" t="n">
         <v>50</v>
@@ -2309,35 +2599,46 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>4096</v>
+        <v>3</v>
       </c>
       <c r="L27" t="n">
         <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="N27" t="n">
-        <v>88.59</v>
+        <v>89.12</v>
       </c>
       <c r="O27" t="n">
         <v>0.01</v>
       </c>
       <c r="P27" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-11_37_47', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 3, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_21-03_27_22', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 3, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>3</v>
+        <v>4096</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U27" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2363,7 +2664,7 @@
         <v>128</v>
       </c>
       <c r="G28" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="H28" t="n">
         <v>50</v>
@@ -2379,7 +2680,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>8192</v>
+        <v>2</v>
       </c>
       <c r="L28" t="n">
         <v>2</v>
@@ -2388,26 +2689,37 @@
         <v>0.29</v>
       </c>
       <c r="N28" t="n">
-        <v>88.45999999999999</v>
+        <v>89.05</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P28" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-07_03_48', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 8192, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_21-02_33_54', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 8192, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R28" t="n">
-        <v>2</v>
+        <v>8192</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U28" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2433,7 +2745,7 @@
         <v>128</v>
       </c>
       <c r="G29" t="n">
-        <v>3000</v>
+        <v>200</v>
       </c>
       <c r="H29" t="n">
         <v>50</v>
@@ -2449,35 +2761,46 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>4096</v>
+        <v>3</v>
       </c>
       <c r="L29" t="n">
         <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="N29" t="n">
-        <v>88.34999999999999</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="P29" t="n">
-        <v>0.63</v>
+        <v>0.45</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_21-03_43_39', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 3000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 3, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-11_55_06', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 200, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 3, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>3</v>
+        <v>4096</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U29" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2496,14 +2819,14 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>NCEK</t>
+          <t>WH</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>128</v>
       </c>
       <c r="G30" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="H30" t="n">
         <v>50</v>
@@ -2519,35 +2842,46 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>8192</v>
+        <v>3</v>
       </c>
       <c r="L30" t="n">
         <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="N30" t="n">
-        <v>88.27</v>
+        <v>88.8</v>
       </c>
       <c r="O30" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="P30" t="n">
-        <v>0.65</v>
+        <v>1.1</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_21-02_56_22', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 8192, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 3000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_21-03_35_12', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 3, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>2</v>
+        <v>4096</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U30" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2566,14 +2900,14 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>WH</t>
+          <t>NCEK</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>128</v>
       </c>
       <c r="G31" t="n">
-        <v>100</v>
+        <v>2500</v>
       </c>
       <c r="H31" t="n">
         <v>50</v>
@@ -2589,35 +2923,46 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
       <c r="L31" t="n">
         <v>2</v>
       </c>
       <c r="M31" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="N31" t="n">
-        <v>88.09999999999999</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="O31" t="n">
         <v>0.03</v>
       </c>
       <c r="P31" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-11_59_40', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 100, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 3, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_21-02_45_01', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 8192, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>3</v>
+        <v>8192</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U31" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2636,7 +2981,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>NCEK</t>
+          <t>WH</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -2659,35 +3004,46 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>8192</v>
+        <v>3</v>
       </c>
       <c r="L32" t="n">
         <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="N32" t="n">
-        <v>88.04000000000001</v>
+        <v>88.59</v>
       </c>
       <c r="O32" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="P32" t="n">
-        <v>0.23</v>
+        <v>1.51</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-07_17_40', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 8192, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-11_37_47', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 3, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>2</v>
+        <v>4096</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U32" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2706,58 +3062,69 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>WH</t>
+          <t>default</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>128</v>
       </c>
       <c r="G33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H33" t="n">
+        <v>10</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>WL_0.3_0.4_0.3</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" t="n">
         <v>0</v>
       </c>
-      <c r="H33" t="n">
-        <v>50</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>mp_spec</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>WL_0_0_1</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
-        <v>4096</v>
-      </c>
-      <c r="L33" t="n">
-        <v>2</v>
-      </c>
       <c r="M33" t="n">
-        <v>0.29</v>
+        <v>0.44</v>
       </c>
       <c r="N33" t="n">
-        <v>86.47</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="P33" t="n">
-        <v>1.5</v>
+        <v>0.37</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-11_05_05', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'mode', 'dataset', 'train_percentage', 'p_epoch', 'f_epoch', 'batch_size', 'ge_layer', 'aug_mode', 'cl_mode', 'skip_pretrain', 'walk_hop', 'eval_freq', 'train_mode', 'print_freq', 'seed', 'ge_mode', 'nce_k', 'num_copies', 'num_samples'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_26-04_55_34', 'cl_mode': 'WL_0.3_0.4_0.3', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'default', 'f_epoch': 10, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 2, 'p_epoch': 1000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 0, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>4096</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U33" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2776,58 +3143,69 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>NCEK</t>
+          <t>default</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>128</v>
       </c>
       <c r="G34" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H34" t="n">
+        <v>10</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>WL_0.3_0.3_0.4</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" t="n">
         <v>0</v>
       </c>
-      <c r="H34" t="n">
-        <v>50</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>mp_spec</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>WL_0_0_1</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
-        <v>4096</v>
-      </c>
-      <c r="L34" t="n">
-        <v>2</v>
-      </c>
       <c r="M34" t="n">
-        <v>0.31</v>
+        <v>0.44</v>
       </c>
       <c r="N34" t="n">
-        <v>84.39</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="O34" t="n">
         <v>0.04</v>
       </c>
       <c r="P34" t="n">
-        <v>1.55</v>
+        <v>0.37</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-09_22_52', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'mode', 'dataset', 'train_percentage', 'p_epoch', 'f_epoch', 'batch_size', 'ge_layer', 'aug_mode', 'cl_mode', 'skip_pretrain', 'walk_hop', 'eval_freq', 'train_mode', 'print_freq', 'seed', 'ge_mode', 'nce_k', 'num_copies', 'num_samples'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_22-17_46_00', 'cl_mode': 'WL_0.3_0.3_0.4', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'default', 'f_epoch': 10, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 2, 'p_epoch': 3000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 0, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R34" t="n">
-        <v>2</v>
+        <v>4096</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U34" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2846,14 +3224,14 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>NCEK</t>
+          <t>WL</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>128</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H35" t="n">
         <v>50</v>
@@ -2865,39 +3243,50 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>WL_0_0_1</t>
+          <t>WL_0.25_0.25_0.5</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>8192</v>
+        <v>2</v>
       </c>
       <c r="L35" t="n">
         <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>0.34</v>
+        <v>0.44</v>
       </c>
       <c r="N35" t="n">
-        <v>84.25</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="P35" t="n">
-        <v>1.89</v>
+        <v>0.37</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-07_48_07', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 8192, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-16_09_32', 'cl_mode': 'WL_0.25_0.25_0.5', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R35" t="n">
-        <v>2</v>
+        <v>4096</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U35" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2916,14 +3305,14 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>WH</t>
+          <t>WL</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>128</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="H36" t="n">
         <v>50</v>
@@ -2935,34 +3324,4176 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t>WL_0.25_0.25_0.5</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" t="n">
+        <v>2</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="N36" t="n">
+        <v>88.52</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-16_13_05', 'cl_mode': 'WL_0.25_0.25_0.5', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R36" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U36" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>128</v>
+      </c>
+      <c r="G37" t="n">
+        <v>500</v>
+      </c>
+      <c r="H37" t="n">
+        <v>50</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>WL_0.25_0.25_0.5</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>2</v>
+      </c>
+      <c r="L37" t="n">
+        <v>2</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="N37" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-16_23_24', 'cl_mode': 'WL_0.25_0.25_0.5', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R37" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U37" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>128</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H38" t="n">
+        <v>10</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>WL_0.4_0.4_0.2</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>2</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N38" t="n">
+        <v>88.45999999999999</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'mode', 'dataset', 'train_percentage', 'p_epoch', 'f_epoch', 'batch_size', 'ge_layer', 'aug_mode', 'cl_mode', 'skip_pretrain', 'walk_hop', 'eval_freq', 'train_mode', 'print_freq', 'seed', 'ge_mode', 'nce_k', 'num_copies', 'num_samples'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_22-17_47_42', 'cl_mode': 'WL_0.4_0.4_0.2', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'default', 'f_epoch': 10, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 2, 'p_epoch': 3000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 0, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R38" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U38" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>NCEK</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>128</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H39" t="n">
+        <v>50</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
           <t>WL_0_0_1</t>
         </is>
       </c>
-      <c r="K36" t="n">
-        <v>4096</v>
-      </c>
-      <c r="L36" t="n">
-        <v>2</v>
-      </c>
-      <c r="M36" t="n">
+      <c r="K39" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" t="n">
+        <v>2</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N39" t="n">
+        <v>88.45999999999999</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-07_03_48', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 8192, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R39" t="n">
+        <v>8192</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U39" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>128</v>
+      </c>
+      <c r="G40" t="n">
+        <v>200</v>
+      </c>
+      <c r="H40" t="n">
+        <v>50</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>WL_0.25_0.25_0.5</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>2</v>
+      </c>
+      <c r="L40" t="n">
+        <v>2</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N40" t="n">
+        <v>88.37</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-16_19_58', 'cl_mode': 'WL_0.25_0.25_0.5', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 200, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R40" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U40" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>128</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H41" t="n">
+        <v>50</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>WL_0.25_0.25_0.5</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>2</v>
+      </c>
+      <c r="L41" t="n">
+        <v>2</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N41" t="n">
+        <v>88.37</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-16_16_32', 'cl_mode': 'WL_0.25_0.25_0.5', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R41" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U41" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>128</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H42" t="n">
+        <v>50</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>WL_0_0_1</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>3</v>
+      </c>
+      <c r="L42" t="n">
+        <v>2</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N42" t="n">
+        <v>88.34999999999999</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_21-03_43_39', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 3000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 3, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R42" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U42" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>NCEK</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>128</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H43" t="n">
+        <v>50</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>WL_0_0_1</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>2</v>
+      </c>
+      <c r="L43" t="n">
+        <v>2</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N43" t="n">
+        <v>88.27</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_21-02_56_22', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 8192, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 3000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R43" t="n">
+        <v>8192</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U43" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>128</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H44" t="n">
+        <v>10</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>WL_0.1_0.8_0.1</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>2</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="N44" t="n">
+        <v>88.13</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'mode', 'dataset', 'train_percentage', 'p_epoch', 'f_epoch', 'batch_size', 'ge_layer', 'aug_mode', 'cl_mode', 'skip_pretrain', 'walk_hop', 'eval_freq', 'train_mode', 'print_freq', 'seed', 'ge_mode', 'nce_k', 'num_copies', 'num_samples'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_26-04_51_39', 'cl_mode': 'WL_0.1_0.8_0.1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'default', 'f_epoch': 10, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 2, 'p_epoch': 1000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 0, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R44" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U44" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>128</v>
+      </c>
+      <c r="G45" t="n">
+        <v>200</v>
+      </c>
+      <c r="H45" t="n">
+        <v>50</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>WL_0.05_0.05_0.9</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>2</v>
+      </c>
+      <c r="L45" t="n">
+        <v>2</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="N45" t="n">
+        <v>88.13</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-17_40_35', 'cl_mode': 'WL_0.05_0.05_0.9', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 200, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R45" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U45" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>128</v>
+      </c>
+      <c r="G46" t="n">
+        <v>100</v>
+      </c>
+      <c r="H46" t="n">
+        <v>50</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>WL_0_0_1</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>3</v>
+      </c>
+      <c r="L46" t="n">
+        <v>2</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N46" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-11_59_40', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 100, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 3, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R46" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U46" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>NCEK</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>128</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H47" t="n">
+        <v>50</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>WL_0_0_1</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>2</v>
+      </c>
+      <c r="L47" t="n">
+        <v>2</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N47" t="n">
+        <v>88.04000000000001</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-07_17_40', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 8192, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R47" t="n">
+        <v>8192</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U47" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>128</v>
+      </c>
+      <c r="G48" t="n">
+        <v>500</v>
+      </c>
+      <c r="H48" t="n">
+        <v>50</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>WL_0.05_0.05_0.9</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>2</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N48" t="n">
+        <v>88.03</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-17_43_37', 'cl_mode': 'WL_0.05_0.05_0.9', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R48" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U48" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>128</v>
+      </c>
+      <c r="G49" t="n">
+        <v>500</v>
+      </c>
+      <c r="H49" t="n">
+        <v>50</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>WL_0.1_0.1_0.8</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>2</v>
+      </c>
+      <c r="L49" t="n">
+        <v>2</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="N49" t="n">
+        <v>87.95</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-17_17_35', 'cl_mode': 'WL_0.1_0.1_0.8', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R49" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U49" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>128</v>
+      </c>
+      <c r="G50" t="n">
+        <v>500</v>
+      </c>
+      <c r="H50" t="n">
+        <v>50</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>WL_0.2_0.2_0.6</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>2</v>
+      </c>
+      <c r="L50" t="n">
+        <v>2</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="N50" t="n">
+        <v>87.54000000000001</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-16_50_29', 'cl_mode': 'WL_0.2_0.2_0.6', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R50" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U50" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>128</v>
+      </c>
+      <c r="G51" t="n">
+        <v>100</v>
+      </c>
+      <c r="H51" t="n">
+        <v>50</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>WL_0.05_0.05_0.9</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>2</v>
+      </c>
+      <c r="L51" t="n">
+        <v>2</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="N51" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-17_46_39', 'cl_mode': 'WL_0.05_0.05_0.9', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 100, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R51" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U51" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>128</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H52" t="n">
+        <v>50</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>WL_0.1_0.1_0.8</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>2</v>
+      </c>
+      <c r="L52" t="n">
+        <v>2</v>
+      </c>
+      <c r="M52" t="n">
         <v>0.44</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N52" t="n">
+        <v>87.44</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-17_10_46', 'cl_mode': 'WL_0.1_0.1_0.8', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R52" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U52" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>128</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H53" t="n">
+        <v>50</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>WL_0.05_0.05_0.9</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>2</v>
+      </c>
+      <c r="L53" t="n">
+        <v>2</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N53" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-17_37_21', 'cl_mode': 'WL_0.05_0.05_0.9', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R53" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U53" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>128</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H54" t="n">
+        <v>50</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>WL_0.1_0.1_0.8</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>2</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N54" t="n">
+        <v>87.39</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-17_07_23', 'cl_mode': 'WL_0.1_0.1_0.8', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R54" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U54" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>128</v>
+      </c>
+      <c r="G55" t="n">
+        <v>200</v>
+      </c>
+      <c r="H55" t="n">
+        <v>50</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>WL_0.2_0.2_0.6</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>2</v>
+      </c>
+      <c r="L55" t="n">
+        <v>2</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N55" t="n">
+        <v>87.04000000000001</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-16_47_04', 'cl_mode': 'WL_0.2_0.2_0.6', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 200, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R55" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U55" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>128</v>
+      </c>
+      <c r="G56" t="n">
+        <v>100</v>
+      </c>
+      <c r="H56" t="n">
+        <v>50</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>WL_0.2_0.2_0.6</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>2</v>
+      </c>
+      <c r="L56" t="n">
+        <v>2</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="N56" t="n">
+        <v>86.81</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-16_53_50', 'cl_mode': 'WL_0.2_0.2_0.6', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 100, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R56" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S56" t="n">
+        <v>2</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U56" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>128</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H57" t="n">
+        <v>50</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>WL_0.05_0.05_0.9</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>2</v>
+      </c>
+      <c r="L57" t="n">
+        <v>2</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="N57" t="n">
+        <v>86.70999999999999</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-17_27_45', 'cl_mode': 'WL_0.05_0.05_0.9', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R57" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U57" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>128</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H58" t="n">
+        <v>50</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>WL_0.1_0.1_0.8</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>2</v>
+      </c>
+      <c r="L58" t="n">
+        <v>2</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N58" t="n">
+        <v>86.69</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-17_00_36', 'cl_mode': 'WL_0.1_0.1_0.8', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R58" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S58" t="n">
+        <v>2</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U58" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>128</v>
+      </c>
+      <c r="G59" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H59" t="n">
+        <v>50</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>WL_0.05_0.05_0.9</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>2</v>
+      </c>
+      <c r="L59" t="n">
+        <v>2</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="N59" t="n">
+        <v>86.56999999999999</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-17_24_22', 'cl_mode': 'WL_0.05_0.05_0.9', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 3000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R59" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S59" t="n">
+        <v>2</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U59" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>128</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H60" t="n">
+        <v>50</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>WL_0.05_0.05_0.9</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>2</v>
+      </c>
+      <c r="L60" t="n">
+        <v>2</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N60" t="n">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P60" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-17_34_10', 'cl_mode': 'WL_0.05_0.05_0.9', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R60" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S60" t="n">
+        <v>2</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U60" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>128</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H61" t="n">
+        <v>50</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>WL_0.1_0.1_0.8</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>2</v>
+      </c>
+      <c r="L61" t="n">
+        <v>2</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N61" t="n">
+        <v>86.48999999999999</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-17_04_00', 'cl_mode': 'WL_0.1_0.1_0.8', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R61" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S61" t="n">
+        <v>2</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U61" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>128</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>50</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>WL_0_0_1</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" t="n">
+        <v>2</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N62" t="n">
+        <v>86.47</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-11_05_05', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R62" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S62" t="n">
+        <v>2</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U62" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>128</v>
+      </c>
+      <c r="G63" t="n">
+        <v>200</v>
+      </c>
+      <c r="H63" t="n">
+        <v>50</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>WL_0.1_0.1_0.8</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>2</v>
+      </c>
+      <c r="L63" t="n">
+        <v>2</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="N63" t="n">
+        <v>86.44</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-17_14_10', 'cl_mode': 'WL_0.1_0.1_0.8', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 200, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R63" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S63" t="n">
+        <v>2</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U63" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>128</v>
+      </c>
+      <c r="G64" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H64" t="n">
+        <v>50</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>WL_0.05_0.05_0.9</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>2</v>
+      </c>
+      <c r="L64" t="n">
+        <v>2</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="N64" t="n">
+        <v>86.31999999999999</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-17_30_58', 'cl_mode': 'WL_0.05_0.05_0.9', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R64" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S64" t="n">
+        <v>2</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U64" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>128</v>
+      </c>
+      <c r="G65" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H65" t="n">
+        <v>10</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>WL_0.05_0.05_0.9</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>2</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="N65" t="n">
+        <v>86.31999999999999</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'mode', 'dataset', 'train_percentage', 'p_epoch', 'f_epoch', 'batch_size', 'ge_layer', 'aug_mode', 'cl_mode', 'skip_pretrain', 'walk_hop', 'eval_freq', 'train_mode', 'print_freq', 'seed', 'ge_mode', 'nce_k', 'num_copies', 'num_samples'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_23-21_14_26', 'cl_mode': 'WL_0.05_0.05_0.9', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'default', 'f_epoch': 10, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 2, 'p_epoch': 3000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 0, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R65" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S65" t="n">
+        <v>2</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U65" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>128</v>
+      </c>
+      <c r="G66" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H66" t="n">
+        <v>50</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>WL_0.2_0.2_0.6</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>2</v>
+      </c>
+      <c r="L66" t="n">
+        <v>2</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="N66" t="n">
+        <v>86.27</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-16_30_11', 'cl_mode': 'WL_0.2_0.2_0.6', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 3000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R66" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S66" t="n">
+        <v>2</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U66" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>128</v>
+      </c>
+      <c r="G67" t="n">
+        <v>100</v>
+      </c>
+      <c r="H67" t="n">
+        <v>50</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>WL_0.25_0.25_0.5</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>2</v>
+      </c>
+      <c r="L67" t="n">
+        <v>2</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N67" t="n">
+        <v>86.26000000000001</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-16_26_47', 'cl_mode': 'WL_0.25_0.25_0.5', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 100, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R67" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S67" t="n">
+        <v>2</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U67" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>128</v>
+      </c>
+      <c r="G68" t="n">
+        <v>100</v>
+      </c>
+      <c r="H68" t="n">
+        <v>50</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>WL_0.1_0.1_0.8</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>2</v>
+      </c>
+      <c r="L68" t="n">
+        <v>2</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="N68" t="n">
+        <v>86.18000000000001</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-17_20_57', 'cl_mode': 'WL_0.1_0.1_0.8', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 100, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R68" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S68" t="n">
+        <v>2</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U68" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>128</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H69" t="n">
+        <v>50</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>WL_0.2_0.2_0.6</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>2</v>
+      </c>
+      <c r="L69" t="n">
+        <v>2</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N69" t="n">
+        <v>86.05</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-16_40_18', 'cl_mode': 'WL_0.2_0.2_0.6', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R69" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S69" t="n">
+        <v>2</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U69" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>128</v>
+      </c>
+      <c r="G70" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H70" t="n">
+        <v>50</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>WL_0.2_0.2_0.6</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>2</v>
+      </c>
+      <c r="L70" t="n">
+        <v>2</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="N70" t="n">
+        <v>85.83</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P70" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-16_33_33', 'cl_mode': 'WL_0.2_0.2_0.6', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R70" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S70" t="n">
+        <v>2</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U70" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>128</v>
+      </c>
+      <c r="G71" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H71" t="n">
+        <v>50</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>WL_0.1_0.1_0.8</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>2</v>
+      </c>
+      <c r="L71" t="n">
+        <v>2</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="N71" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-16_57_14', 'cl_mode': 'WL_0.1_0.1_0.8', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 3000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R71" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S71" t="n">
+        <v>2</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U71" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>128</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H72" t="n">
+        <v>50</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>WL_0.2_0.2_0.6</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>2</v>
+      </c>
+      <c r="L72" t="n">
+        <v>2</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N72" t="n">
+        <v>85.23999999999999</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-16_36_56', 'cl_mode': 'WL_0.2_0.2_0.6', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R72" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S72" t="n">
+        <v>2</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U72" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>128</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H73" t="n">
+        <v>50</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>WL_0.2_0.2_0.6</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>2</v>
+      </c>
+      <c r="L73" t="n">
+        <v>2</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N73" t="n">
+        <v>84.70999999999999</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_24-16_43_43', 'cl_mode': 'WL_0.2_0.2_0.6', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R73" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S73" t="n">
+        <v>2</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U73" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>128</v>
+      </c>
+      <c r="G74" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H74" t="n">
+        <v>10</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>WL_0.35_0.35_0.3</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N74" t="n">
+        <v>84.70999999999999</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'mode', 'dataset', 'train_percentage', 'p_epoch', 'f_epoch', 'batch_size', 'ge_layer', 'aug_mode', 'cl_mode', 'skip_pretrain', 'walk_hop', 'eval_freq', 'train_mode', 'print_freq', 'seed', 'ge_mode', 'nce_k', 'num_copies', 'num_samples'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_20-10_15_42', 'cl_mode': 'WL_0.35_0.35_0.3', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'default', 'f_epoch': 10, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 2, 'p_epoch': 3000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 0, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R74" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S74" t="n">
+        <v>2</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U74" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>NCEK</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>128</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>50</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>WL_0_0_1</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>2</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N75" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-09_22_52', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R75" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S75" t="n">
+        <v>2</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U75" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>NCEK</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>128</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>50</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>WL_0_0_1</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>2</v>
+      </c>
+      <c r="L76" t="n">
+        <v>2</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N76" t="n">
+        <v>84.25</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-07_48_07', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 8192, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R76" t="n">
+        <v>8192</v>
+      </c>
+      <c r="S76" t="n">
+        <v>2</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U76" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>WH</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>128</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>50</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>WL_0_0_1</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>3</v>
+      </c>
+      <c r="L77" t="n">
+        <v>2</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N77" t="n">
         <v>81.5</v>
       </c>
-      <c r="O36" t="n">
+      <c r="O77" t="n">
         <v>0.02</v>
       </c>
-      <c r="P36" t="n">
+      <c r="P77" t="n">
         <v>0.27</v>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-12_25_54', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 3, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
-      <c r="R36" t="n">
-        <v>3</v>
+      <c r="R77" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S77" t="n">
+        <v>2</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U77" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>128</v>
+      </c>
+      <c r="G78" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H78" t="n">
+        <v>10</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>WL_0.05_0.05_0.9</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N78" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'mode', 'dataset', 'train_percentage', 'p_epoch', 'f_epoch', 'batch_size', 'ge_layer', 'aug_mode', 'cl_mode', 'skip_pretrain', 'walk_hop', 'eval_freq', 'train_mode', 'print_freq', 'seed', 'ge_mode', 'nce_k', 'num_copies', 'num_samples'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_18-17_29_01', 'cl_mode': 'WL_0.05_0.05_0.9', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'default', 'f_epoch': 10, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 2, 'p_epoch': 3000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 0, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R78" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S78" t="n">
+        <v>2</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U78" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>128</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>50</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>WL_0.1_0.1_0.8</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>2</v>
+      </c>
+      <c r="L79" t="n">
+        <v>2</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N79" t="n">
+        <v>79.19</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_20-12_42_36', 'cl_mode': 'WL_0.1_0.1_0.8', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R79" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S79" t="n">
+        <v>2</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U79" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>128</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>50</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>WL_0.25_0.25_0.5</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>2</v>
+      </c>
+      <c r="L80" t="n">
+        <v>2</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N80" t="n">
+        <v>79.19</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_20-12_34_59', 'cl_mode': 'WL_0.25_0.25_0.5', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R80" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S80" t="n">
+        <v>2</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U80" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>128</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>50</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>WL_0.05_0.05_0.9</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>2</v>
+      </c>
+      <c r="L81" t="n">
+        <v>2</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N81" t="n">
+        <v>79.19</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_20-12_57_02', 'cl_mode': 'WL_0.05_0.05_0.9', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R81" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S81" t="n">
+        <v>2</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U81" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>128</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>50</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>WL_0.33_0.33_0.33</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>2</v>
+      </c>
+      <c r="L82" t="n">
+        <v>2</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N82" t="n">
+        <v>79.19</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_20-12_31_06', 'cl_mode': 'WL_0.33_0.33_0.33', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R82" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S82" t="n">
+        <v>2</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U82" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>128</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>50</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>WL_0.025_0.025_0.95</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>2</v>
+      </c>
+      <c r="L83" t="n">
+        <v>2</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N83" t="n">
+        <v>79.19</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_20-13_02_44', 'cl_mode': 'WL_0.025_0.025_0.95', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R83" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S83" t="n">
+        <v>2</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U83" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>128</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>50</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>WL_0.2_0.2_0.6</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>2</v>
+      </c>
+      <c r="L84" t="n">
+        <v>2</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N84" t="n">
+        <v>79.19</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_20-12_38_45', 'cl_mode': 'WL_0.2_0.2_0.6', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R84" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S84" t="n">
+        <v>2</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U84" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>128</v>
+      </c>
+      <c r="G85" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H85" t="n">
+        <v>10</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>WL_0.25_0.25_0.5</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N85" t="n">
+        <v>79.19</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'mode', 'dataset', 'train_percentage', 'p_epoch', 'f_epoch', 'batch_size', 'ge_layer', 'aug_mode', 'cl_mode', 'skip_pretrain', 'walk_hop', 'eval_freq', 'train_mode', 'print_freq', 'seed', 'ge_mode', 'nce_k', 'num_copies', 'num_samples'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_20-10_12_49', 'cl_mode': 'WL_0.25_0.25_0.5', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'default', 'f_epoch': 10, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 2, 'p_epoch': 3000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 0, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R85" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S85" t="n">
+        <v>2</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U85" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>128</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H86" t="n">
+        <v>10</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>WL_0_1_0</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>2</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N86" t="n">
+        <v>79.19</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'mode', 'dataset', 'train_percentage', 'p_epoch', 'f_epoch', 'batch_size', 'ge_layer', 'aug_mode', 'cl_mode', 'skip_pretrain', 'walk_hop', 'eval_freq', 'train_mode', 'print_freq', 'seed', 'ge_mode', 'nce_k', 'num_copies', 'num_samples'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_26-04_48_20', 'cl_mode': 'WL_0_1_0', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'default', 'f_epoch': 10, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 2, 'p_epoch': 1000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 0, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R86" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S86" t="n">
+        <v>2</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U86" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>dblp</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>128</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H87" t="n">
+        <v>10</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>WL_0.2_0.6_0.2</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>2</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="N87" t="n">
+        <v>76.53</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P87" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'mode', 'dataset', 'train_percentage', 'p_epoch', 'f_epoch', 'batch_size', 'ge_layer', 'aug_mode', 'cl_mode', 'skip_pretrain', 'walk_hop', 'eval_freq', 'train_mode', 'print_freq', 'seed', 'ge_mode', 'nce_k', 'num_copies', 'num_samples'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '03_26-04_47_40', 'cl_mode': 'WL_0.2_0.6_0.2', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'default', 'f_epoch': 10, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 2, 'p_epoch': 1000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 0, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="R87" t="n">
+        <v>4096</v>
+      </c>
+      <c r="S87" t="n">
+        <v>2</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>moco</t>
+        </is>
+      </c>
+      <c r="U87" t="n">
+        <v>2000</v>
       </c>
     </row>
   </sheetData>
